--- a/Field_Survey_Template_Latur.xlsx
+++ b/Field_Survey_Template_Latur.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,20 +28,25 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00334155"/>
-      <sz val="9"/>
+      <color rgb="001E293B"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -53,26 +58,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F5132"/>
-        <bgColor rgb="000F5132"/>
+        <fgColor rgb="001E3A8A"/>
+        <bgColor rgb="001E3A8A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2E8F0"/>
-        <bgColor rgb="00E2E8F0"/>
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00107C41"/>
-        <bgColor rgb="00107C41"/>
+        <fgColor rgb="000F766E"/>
+        <bgColor rgb="000F766E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0FDF4"/>
-        <bgColor rgb="00F0FDF4"/>
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
   </fills>
@@ -108,15 +113,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -484,178 +489,382 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:BH4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="24" customWidth="1" min="21" max="21"/>
-    <col width="24" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="34" customWidth="1" min="25" max="25"/>
-    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="21" customWidth="1" min="29" max="29"/>
+    <col width="21" customWidth="1" min="30" max="30"/>
+    <col width="28" customWidth="1" min="31" max="31"/>
+    <col width="28" customWidth="1" min="32" max="32"/>
+    <col width="25" customWidth="1" min="33" max="33"/>
+    <col width="11" customWidth="1" min="34" max="34"/>
+    <col width="16" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="23" customWidth="1" min="37" max="37"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="21" customWidth="1" min="39" max="39"/>
+    <col width="16" customWidth="1" min="40" max="40"/>
+    <col width="21" customWidth="1" min="41" max="41"/>
+    <col width="14" customWidth="1" min="42" max="42"/>
+    <col width="19" customWidth="1" min="43" max="43"/>
+    <col width="14" customWidth="1" min="44" max="44"/>
+    <col width="19" customWidth="1" min="45" max="45"/>
+    <col width="17" customWidth="1" min="46" max="46"/>
+    <col width="22" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="48" max="48"/>
+    <col width="19" customWidth="1" min="49" max="49"/>
+    <col width="14" customWidth="1" min="50" max="50"/>
+    <col width="20" customWidth="1" min="51" max="51"/>
+    <col width="26" customWidth="1" min="52" max="52"/>
+    <col width="20" customWidth="1" min="53" max="53"/>
+    <col width="30" customWidth="1" min="54" max="54"/>
+    <col width="20" customWidth="1" min="55" max="55"/>
+    <col width="29" customWidth="1" min="56" max="56"/>
+    <col width="20" customWidth="1" min="57" max="57"/>
+    <col width="17" customWidth="1" min="58" max="58"/>
+    <col width="20" customWidth="1" min="59" max="59"/>
+    <col width="33" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GSDA MAHARASHTRA — 20-COLUMN FIELD SURVEY INPUT TEMPLATE (LATUR DISTRICT)</t>
+          <t>GSDA MAHARASHTRA — GROUNDWATER SURVEY &amp; MONITORING MASTER TEMPLATE (LATUR DISTRICT)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Note: Fill columns A to Z. On Upload, the system auto-calculates 10K Sheet No, Toposheet No, Gat No, Village, Taluka, Hydraulics, Drawdowns, and Crop Drafts into Form 1, Form 2, All Collected Data, and MRSAC Sheet.</t>
+          <t>INSTRUCTIONS: Fill survey records from Row 4 downwards. 'Well No' is the unique sequential well number (e.g. 01). 'Gat No' can be left blank (auto-calculated from GPS LatLong). Dedicated separate columns are provided for Winter and Summer recuperation, individual crops, and 5-layer basalt lithology.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sr_No</t>
+          <t>Sr.No.</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Survey_Date</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Geologist_Name</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Owner_Name</t>
+          <t>Geologist Name</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Survey_Category</t>
+          <t>Mapsheetno</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Well No</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Gat No</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Gat_No</t>
+          <t>Type of well</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Well_Type</t>
+          <t>Well Owner</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Diameter_m</t>
+          <t>Taluka Name</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Depth_m</t>
+          <t>Village Name</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Parapet_Height_m</t>
+          <t>Population</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>SWL_Winter_m</t>
+          <t>LatLong</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>SWL_Summer_m</t>
+          <t>Altitude</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>Pump_Type</t>
+          <t>Measuring Point</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Pump_HP</t>
+          <t>Parapet (m)</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>Pump_Hrs_Winter</t>
+          <t>Diameter (m)</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>Pump_Hrs_Summer</t>
+          <t>effec. Dia</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>Recuperation_Hrs</t>
+          <t>Depth</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>Cultivable_Area_Ha</t>
+          <t>Curbing (m)</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>Kharif_Crops</t>
+          <t>Type of curbing</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>Rabi_Crops</t>
+          <t>Year of Construction</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>Perennial_Crops</t>
+          <t>DwL</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>Summer_Crops</t>
+          <t>Winter (SWL)</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>Lithology_Strata</t>
+          <t>Summer (SWL)</t>
         </is>
       </c>
       <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>Type of Pump</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Mode of Power</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>Winter pumping hrs</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>Summer pumping hrs</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>winter T req recuperation</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>Summer T req recuperation</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Project Irri(PT/MInor)</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr">
+        <is>
+          <t>Distance c</t>
+        </is>
+      </c>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t>Cultivable land (Ha)</t>
+        </is>
+      </c>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Kharif Crop 1</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Kharif Area 1 (Ha)</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>Kharif Crop 2</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>Kharif Area 2 (Ha)</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>Rabi Crop 1</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>Rabi Area 1 (Ha)</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Rabi Crop 2</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>Rabi Area 2 (Ha)</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>Perennial Crop</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Perennial Area (Ha)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Summer Crop</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>Summer Area (Ha)</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Lithology 1</t>
+        </is>
+      </c>
+      <c r="AY3" s="3" t="inlineStr">
+        <is>
+          <t>Litho Depth 1 (m)</t>
+        </is>
+      </c>
+      <c r="AZ3" s="3" t="inlineStr">
+        <is>
+          <t>Lithology 2</t>
+        </is>
+      </c>
+      <c r="BA3" s="3" t="inlineStr">
+        <is>
+          <t>Litho Depth 2 (m)</t>
+        </is>
+      </c>
+      <c r="BB3" s="3" t="inlineStr">
+        <is>
+          <t>Lithology 3</t>
+        </is>
+      </c>
+      <c r="BC3" s="3" t="inlineStr">
+        <is>
+          <t>Litho Depth 3 (m)</t>
+        </is>
+      </c>
+      <c r="BD3" s="3" t="inlineStr">
+        <is>
+          <t>Lithology 4</t>
+        </is>
+      </c>
+      <c r="BE3" s="3" t="inlineStr">
+        <is>
+          <t>Litho Depth 4 (m)</t>
+        </is>
+      </c>
+      <c r="BF3" s="3" t="inlineStr">
+        <is>
+          <t>Lithology 5</t>
+        </is>
+      </c>
+      <c r="BG3" s="3" t="inlineStr">
+        <is>
+          <t>Litho Depth 5 (m)</t>
+        </is>
+      </c>
+      <c r="BH3" s="3" t="inlineStr">
         <is>
           <t>Well_Remarks</t>
         </is>
@@ -667,192 +876,236 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Dr. Farjana Birajdar</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Mahananda Somanath Kothane</t>
+          <t>S. M. Sabale</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Irrigation</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>17.598239</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>76.052817</v>
-      </c>
+          <t>E43O05M</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>Dug Well</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Dug Well</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>10.66</v>
+          <t>Balaji Patil</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Latur</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Latur Rural</t>
+        </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>9.140000000000001</v>
+        <v>3100</v>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>18.408800, 76.560400</t>
+        </is>
       </c>
       <c r="N4" s="4" t="n">
-        <v>10.66</v>
+        <v>631</v>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
+          <t>Top of Parapet</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>Masonry</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>2019</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="X4" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z4" s="5" t="inlineStr">
+        <is>
           <t>Submersible</t>
         </is>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="AA4" s="5" t="inlineStr">
+        <is>
+          <t>Electric</t>
+        </is>
+      </c>
+      <c r="AB4" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="Q4" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" s="4" t="n">
+      <c r="AC4" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="S4" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="U4" s="5" t="inlineStr">
-        <is>
-          <t>Tur: 0.8, Udid: 0.8</t>
-        </is>
-      </c>
-      <c r="V4" s="5" t="inlineStr">
-        <is>
-          <t>Wheat: 0.8, Jowar: 0.8</t>
-        </is>
-      </c>
-      <c r="W4" s="5" t="inlineStr"/>
-      <c r="X4" s="5" t="inlineStr"/>
-      <c r="Y4" s="5" t="inlineStr">
-        <is>
-          <t>Soil: 0.5m, W.Basalt: 3m, J.Basalt: 9m, M.Basalt: 10.66m</t>
-        </is>
-      </c>
-      <c r="Z4" s="5" t="inlineStr">
-        <is>
-          <t>Seasonal</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="4" t="n">
+      <c r="AD4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>17/03/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>V. N. Nimbalkar</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Gram Panchayat Water Supply</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>PWS</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>17.596496</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>76.052817</v>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Dug Well</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="L5" s="4" t="n">
+      <c r="AE4" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF4" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG4" s="5" t="inlineStr">
+        <is>
+          <t>Minor Irrigation</t>
+        </is>
+      </c>
+      <c r="AH4" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="AI4" s="5" t="inlineStr">
+        <is>
+          <t>Manjara Canal</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="AK4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL4" s="5" t="inlineStr">
+        <is>
+          <t>Soybean</t>
+        </is>
+      </c>
+      <c r="AM4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" s="5" t="inlineStr">
+        <is>
+          <t>Tur</t>
+        </is>
+      </c>
+      <c r="AO4" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP4" s="5" t="inlineStr">
+        <is>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="AQ4" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR4" s="5" t="inlineStr">
+        <is>
+          <t>Gram</t>
+        </is>
+      </c>
+      <c r="AS4" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="M5" s="4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>Submersible</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="S5" s="4" t="n">
+      <c r="AT4" s="5" t="inlineStr">
+        <is>
+          <t>Sugarcane</t>
+        </is>
+      </c>
+      <c r="AU4" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV4" s="5" t="inlineStr"/>
+      <c r="AW4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" s="5" t="inlineStr">
+        <is>
+          <t>Soil</t>
+        </is>
+      </c>
+      <c r="AY4" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AZ4" s="5" t="inlineStr">
+        <is>
+          <t>Highly Weathered Basalt</t>
+        </is>
+      </c>
+      <c r="BA4" s="4" t="n">
         <v>3.5</v>
       </c>
-      <c r="T5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="5" t="inlineStr"/>
-      <c r="V5" s="5" t="inlineStr"/>
-      <c r="W5" s="5" t="inlineStr"/>
-      <c r="X5" s="5" t="inlineStr"/>
-      <c r="Y5" s="5" t="inlineStr">
-        <is>
-          <t>Soil: 1m, W.Basalt: 4m, J.Basalt: 10m, M.Basalt: 12.5m</t>
-        </is>
-      </c>
-      <c r="Z5" s="5" t="inlineStr">
-        <is>
-          <t>Drinking Water Source</t>
+      <c r="BB4" s="5" t="inlineStr">
+        <is>
+          <t>Moderately Weathered Basalt</t>
+        </is>
+      </c>
+      <c r="BC4" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BD4" s="5" t="inlineStr">
+        <is>
+          <t>Fractured / Jointed Basalt</t>
+        </is>
+      </c>
+      <c r="BE4" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF4" s="5" t="inlineStr">
+        <is>
+          <t>Massive Basalt</t>
+        </is>
+      </c>
+      <c r="BG4" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH4" s="5" t="inlineStr">
+        <is>
+          <t>Adequate yield throughout year</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="A2:Z2"/>
+    <mergeCell ref="A1:BH1"/>
+    <mergeCell ref="A2:BH2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Field_Survey_Template_Latur.xlsx
+++ b/Field_Survey_Template_Latur.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BJ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -557,14 +557,14 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GSDA MAHARASHTRA — GROUNDWATER SURVEY &amp; MONITORING MASTER TEMPLATE (LATUR DISTRICT)</t>
+          <t>GSDA MAHARASHTRA - GROUNDWATER SURVEY &amp; MONITORING MASTER TEMPLATE (OFFICIAL MASTER DISTRICT)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>INSTRUCTIONS: Fill survey records from Row 4 downwards. 'Well No' is the unique sequential well number (e.g. 01). 'Gat No' can be left blank (auto-calculated from GPS LatLong). Dedicated separate columns are provided for Winter and Summer recuperation, individual crops, and 5-layer basalt lithology.</t>
+          <t>INSTRUCTIONS: Fill survey records from Row 4 downwards. 'Well No' is the unique sequential well number (e.g. 01). 'Form Type (Irrigation/PWS)' specifies Irrigation or PWS scheme. 'Mapsheetno' is 10K sheet code (e.g. E43Q02Q). 'Toposheet No.' is SOI 50K Sheet (e.g. 56 C/02). Dedicated separate columns are provided for Winter and Summer recuperation, individual crops, DwL, Curbing (m), Year of Construction, and 5-layer basalt lithology.</t>
         </is>
       </c>
     </row>
@@ -606,265 +606,275 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
+          <t>Form Type (Irrigation/PWS)</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>Type of well</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Well Owner</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Taluka Name</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Village Name</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Population</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>LatLong</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Altitude</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>Measuring Point</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>Parapet (m)</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>Diameter (m)</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>effec. Dia</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>Depth</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>Curbing (m)</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>Type of curbing</t>
         </is>
       </c>
-      <c r="V3" s="3" t="inlineStr">
+      <c r="W3" s="3" t="inlineStr">
         <is>
           <t>Year of Construction</t>
         </is>
       </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>DwL</t>
         </is>
       </c>
-      <c r="X3" s="3" t="inlineStr">
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>Winter (SWL)</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>Summer (SWL)</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>Type of Pump</t>
         </is>
       </c>
-      <c r="AA3" s="3" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>Mode of Power</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr">
+      <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="AC3" s="3" t="inlineStr">
+      <c r="AD3" s="3" t="inlineStr">
         <is>
           <t>Winter pumping hrs</t>
         </is>
       </c>
-      <c r="AD3" s="3" t="inlineStr">
+      <c r="AE3" s="3" t="inlineStr">
         <is>
           <t>Summer pumping hrs</t>
         </is>
       </c>
-      <c r="AE3" s="3" t="inlineStr">
+      <c r="AF3" s="3" t="inlineStr">
         <is>
           <t>winter T req recuperation</t>
         </is>
       </c>
-      <c r="AF3" s="3" t="inlineStr">
+      <c r="AG3" s="3" t="inlineStr">
         <is>
           <t>Summer T req recuperation</t>
         </is>
       </c>
-      <c r="AG3" s="3" t="inlineStr">
+      <c r="AH3" s="3" t="inlineStr">
         <is>
           <t>Project Irri(PT/MInor)</t>
         </is>
       </c>
-      <c r="AH3" s="3" t="inlineStr">
+      <c r="AI3" s="3" t="inlineStr">
         <is>
           <t>Distance</t>
         </is>
       </c>
-      <c r="AI3" s="3" t="inlineStr">
+      <c r="AJ3" s="3" t="inlineStr">
         <is>
           <t>Canal</t>
         </is>
       </c>
-      <c r="AJ3" s="3" t="inlineStr">
+      <c r="AK3" s="3" t="inlineStr">
         <is>
           <t>Distance c</t>
         </is>
       </c>
-      <c r="AK3" s="3" t="inlineStr">
+      <c r="AL3" s="3" t="inlineStr">
         <is>
           <t>Cultivable land (Ha)</t>
         </is>
       </c>
-      <c r="AL3" s="3" t="inlineStr">
+      <c r="AM3" s="3" t="inlineStr">
         <is>
           <t>Kharif Crop 1</t>
         </is>
       </c>
-      <c r="AM3" s="3" t="inlineStr">
+      <c r="AN3" s="3" t="inlineStr">
         <is>
           <t>Kharif Area 1 (Ha)</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>Kharif Crop 2</t>
         </is>
       </c>
-      <c r="AO3" s="3" t="inlineStr">
+      <c r="AP3" s="3" t="inlineStr">
         <is>
           <t>Kharif Area 2 (Ha)</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
+      <c r="AQ3" s="3" t="inlineStr">
         <is>
           <t>Rabi Crop 1</t>
         </is>
       </c>
-      <c r="AQ3" s="3" t="inlineStr">
+      <c r="AR3" s="3" t="inlineStr">
         <is>
           <t>Rabi Area 1 (Ha)</t>
         </is>
       </c>
-      <c r="AR3" s="3" t="inlineStr">
+      <c r="AS3" s="3" t="inlineStr">
         <is>
           <t>Rabi Crop 2</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
+      <c r="AT3" s="3" t="inlineStr">
         <is>
           <t>Rabi Area 2 (Ha)</t>
         </is>
       </c>
-      <c r="AT3" s="3" t="inlineStr">
+      <c r="AU3" s="3" t="inlineStr">
         <is>
           <t>Perennial Crop</t>
         </is>
       </c>
-      <c r="AU3" s="3" t="inlineStr">
+      <c r="AV3" s="3" t="inlineStr">
         <is>
           <t>Perennial Area (Ha)</t>
         </is>
       </c>
-      <c r="AV3" s="3" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>Summer Crop</t>
         </is>
       </c>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AX3" s="3" t="inlineStr">
         <is>
           <t>Summer Area (Ha)</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr">
+      <c r="AY3" s="3" t="inlineStr">
         <is>
           <t>Lithology 1</t>
         </is>
       </c>
-      <c r="AY3" s="3" t="inlineStr">
+      <c r="AZ3" s="3" t="inlineStr">
         <is>
           <t>Litho Depth 1 (m)</t>
         </is>
       </c>
-      <c r="AZ3" s="3" t="inlineStr">
+      <c r="BA3" s="3" t="inlineStr">
         <is>
           <t>Lithology 2</t>
         </is>
       </c>
-      <c r="BA3" s="3" t="inlineStr">
+      <c r="BB3" s="3" t="inlineStr">
         <is>
           <t>Litho Depth 2 (m)</t>
         </is>
       </c>
-      <c r="BB3" s="3" t="inlineStr">
+      <c r="BC3" s="3" t="inlineStr">
         <is>
           <t>Lithology 3</t>
         </is>
       </c>
-      <c r="BC3" s="3" t="inlineStr">
+      <c r="BD3" s="3" t="inlineStr">
         <is>
           <t>Litho Depth 3 (m)</t>
         </is>
       </c>
-      <c r="BD3" s="3" t="inlineStr">
+      <c r="BE3" s="3" t="inlineStr">
         <is>
           <t>Lithology 4</t>
         </is>
       </c>
-      <c r="BE3" s="3" t="inlineStr">
+      <c r="BF3" s="3" t="inlineStr">
         <is>
           <t>Litho Depth 4 (m)</t>
         </is>
       </c>
-      <c r="BF3" s="3" t="inlineStr">
+      <c r="BG3" s="3" t="inlineStr">
         <is>
           <t>Lithology 5</t>
         </is>
       </c>
-      <c r="BG3" s="3" t="inlineStr">
+      <c r="BH3" s="3" t="inlineStr">
         <is>
           <t>Litho Depth 5 (m)</t>
         </is>
       </c>
-      <c r="BH3" s="3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>Toposheet No.</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>Well_Remarks</t>
         </is>
@@ -886,12 +896,12 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>S. M. Sabale</t>
+          <t>V. N. Nimbalkar</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>E43O05M</t>
+          <t>E43Q02Q</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -902,203 +912,223 @@
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr">
         <is>
+          <t>Irrigation</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
           <t>Dug Well</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>Balaji Patil</t>
-        </is>
-      </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>Latur</t>
+          <t>Dhanabai Rathod</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>Latur Rural</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>3100</v>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>18.408800, 76.560400</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>631</v>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
+          <t>South Solapur</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Akkalkot Rural</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>2450</v>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>17.477739, 76.170122</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>465</v>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>Top of Parapet</t>
         </is>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="Q4" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q4" s="4" t="n">
-        <v>12</v>
-      </c>
       <c r="R4" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S4" s="4" t="n">
         <v>14</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" s="5" t="inlineStr">
+        <v>13</v>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
         <is>
           <t>Masonry</t>
         </is>
       </c>
-      <c r="V4" s="4" t="n">
-        <v>2019</v>
-      </c>
       <c r="W4" s="4" t="n">
-        <v>7.5</v>
+        <v>2018</v>
       </c>
       <c r="X4" s="4" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="Y4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z4" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="Z4" s="5" t="inlineStr">
+      <c r="AA4" s="5" t="inlineStr">
         <is>
           <t>Submersible</t>
         </is>
       </c>
-      <c r="AA4" s="5" t="inlineStr">
+      <c r="AB4" s="4" t="inlineStr">
         <is>
           <t>Electric</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="n">
+      <c r="AC4" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AC4" s="4" t="n">
+      <c r="AD4" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD4" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="AE4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="AF4" s="4" t="n">
+      <c r="AG4" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="AG4" s="5" t="inlineStr">
-        <is>
-          <t>Minor Irrigation</t>
-        </is>
-      </c>
-      <c r="AH4" s="4" t="n">
-        <v>400</v>
+      <c r="AH4" s="4" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
       </c>
       <c r="AI4" s="5" t="inlineStr">
         <is>
-          <t>Manjara Canal</t>
-        </is>
-      </c>
-      <c r="AJ4" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="AK4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL4" s="5" t="inlineStr">
+          <t>500m</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+      <c r="AK4" s="4" t="inlineStr">
+        <is>
+          <t>1km</t>
+        </is>
+      </c>
+      <c r="AL4" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM4" s="4" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="AN4" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO4" s="4" t="inlineStr">
         <is>
           <t>Soybean</t>
         </is>
       </c>
-      <c r="AM4" s="4" t="n">
+      <c r="AP4" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ4" s="4" t="inlineStr">
+        <is>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="AR4" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AS4" s="4" t="inlineStr">
+        <is>
+          <t>Gram</t>
+        </is>
+      </c>
+      <c r="AT4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AV4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AX4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="4" t="inlineStr">
+        <is>
+          <t>Soil</t>
+        </is>
+      </c>
+      <c r="AZ4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="AN4" s="5" t="inlineStr">
-        <is>
-          <t>Tur</t>
-        </is>
-      </c>
-      <c r="AO4" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP4" s="5" t="inlineStr">
-        <is>
-          <t>Wheat</t>
-        </is>
-      </c>
-      <c r="AQ4" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AR4" s="5" t="inlineStr">
-        <is>
-          <t>Gram</t>
-        </is>
-      </c>
-      <c r="AS4" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AT4" s="5" t="inlineStr">
-        <is>
-          <t>Sugarcane</t>
-        </is>
-      </c>
-      <c r="AU4" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV4" s="5" t="inlineStr"/>
-      <c r="AW4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" s="5" t="inlineStr">
-        <is>
-          <t>Soil</t>
-        </is>
-      </c>
-      <c r="AY4" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AZ4" s="5" t="inlineStr">
+      <c r="BA4" s="4" t="inlineStr">
         <is>
           <t>Highly Weathered Basalt</t>
         </is>
       </c>
-      <c r="BA4" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BB4" s="5" t="inlineStr">
+      <c r="BB4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC4" s="4" t="inlineStr">
         <is>
           <t>Moderately Weathered Basalt</t>
         </is>
       </c>
-      <c r="BC4" s="4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BD4" s="5" t="inlineStr">
-        <is>
-          <t>Fractured / Jointed Basalt</t>
-        </is>
-      </c>
-      <c r="BE4" s="4" t="n">
+      <c r="BD4" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="BF4" s="5" t="inlineStr">
+      <c r="BE4" s="4" t="inlineStr">
+        <is>
+          <t>Fractured/ Jointed Basalt</t>
+        </is>
+      </c>
+      <c r="BF4" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG4" s="4" t="inlineStr">
         <is>
           <t>Massive Basalt</t>
         </is>
       </c>
-      <c r="BG4" s="4" t="n">
-        <v>14</v>
-      </c>
       <c r="BH4" s="5" t="inlineStr">
         <is>
-          <t>Adequate yield throughout year</t>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>56 C/02</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>Seasonal yield</t>
         </is>
       </c>
     </row>
